--- a/Cardiologie/Excel/cardio_13.xlsx
+++ b/Cardiologie/Excel/cardio_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F645C142-0B7F-47A1-AD78-6BA9EF2CA758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009F1B04-ACF9-4A5A-BC15-F888E31896F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,16 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="213">
-  <si>
-    <t>numero</t>
-  </si>
-  <si>
-    <t>proposition</t>
-  </si>
-  <si>
-    <t>reponse</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
   <si>
     <t>Les acrosyndromes vasculaires sont toujours secondaires à une autre pathologie vasculaire.</t>
   </si>
@@ -583,9 +574,6 @@
     <t>Les engelures sont des lésions cutanées inflammatoires liées au froid et à l’humidité.</t>
   </si>
   <si>
-    <t>Les engelures consistent en une vraie congélation tissulaire.</t>
-  </si>
-  <si>
     <t>Les engelures surviennent uniquement en hiver lorsqu’il gèle.</t>
   </si>
   <si>
@@ -616,9 +604,6 @@
     <t>Les engelures évoluent vers une guérison spontanée progressive et généralement ne récidivent pas.</t>
   </si>
   <si>
-    <t>Il n’existe pas de traitement vraiment efficace contre les engelures.</t>
-  </si>
-  <si>
     <t>Les vasoconstricteurs et les antagonistes calciques peuvent être utiles dans le traitement des engelures.</t>
   </si>
   <si>
@@ -655,26 +640,39 @@
     <t>L’apoplexie digitale est un processus très douloureux de début progressif.</t>
   </si>
   <si>
-    <t>Faux</t>
-  </si>
-  <si>
-    <t>Vrai</t>
+    <t>Les engelures consistent en une VRAIe congélation tissulaire.</t>
+  </si>
+  <si>
+    <t>Il n’existe pas de traitement VRAIment efficace contre les engelures.</t>
+  </si>
+  <si>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Proposition</t>
+  </si>
+  <si>
+    <t>Reponse</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -690,27 +688,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -719,11 +702,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1029,2312 +1012,2324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="193.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="193.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C30" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C32" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C33" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C34" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C37" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C39" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C41" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C47" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C49" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C50" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C51" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C52" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C53" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C54" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C55" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C57" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C58" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C59" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C61" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C62" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C64" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C65" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C69" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C70" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C71" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C72" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C73" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C74" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C75" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="B76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C76" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="B77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C77" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C78" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C79" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="B80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C80" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C81" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="B82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C82" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="B83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="B84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C84" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="B85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C85" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C86" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C87" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C88" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C89" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C92" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="B93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C93" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="C94" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C95" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="B96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C96" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C97" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="B98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C98" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="B99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C99" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="B100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C100" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="B101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C101" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C102" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="B103" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C103" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="B104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C104" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="B105" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C105" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="B106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C106" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="B107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C107" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="B108" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C108" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="B109" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C109" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="B110" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C110" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="B111" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C111" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="B112" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C112" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="B113" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C113" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="B114" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C114" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C115" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="B116" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C116" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="B117" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C117" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="B118" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C118" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="B119" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C119" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="B120" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C120" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="C121" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="B122" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C122" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="B123" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C123" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="B124" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="C124" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="B125" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C125" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="B126" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C126" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="B127" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="C127" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
         <v>127</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="B128" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="C128" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
         <v>128</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="B129" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C129" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="B130" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C130" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="B131" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C131" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="B132" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C132" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="B133" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="C133" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="B134" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C134" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
+      <c r="B135" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="C135" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="B136" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="C136" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="B137" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="C137" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="B138" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="C138" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="B139" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="C139" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="B140" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="C140" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="B141" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C141" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="B142" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="C142" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="B143" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="C143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="B144" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="C144" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
+      <c r="B145" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="C145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="B146" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="C146" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="B147" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="C147" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
         <v>147</v>
       </c>
-      <c r="C146" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="B148" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C148" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
         <v>148</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="B149" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C149" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
         <v>149</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="B150" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="C150" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
         <v>150</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="B151" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="C151" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
         <v>151</v>
       </c>
-      <c r="C150" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
+      <c r="B152" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="C152" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
         <v>152</v>
       </c>
-      <c r="C151" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="B153" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="C153" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
         <v>153</v>
       </c>
-      <c r="C152" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
+      <c r="B154" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="C154" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
         <v>154</v>
       </c>
-      <c r="C153" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="B155" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="C155" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
         <v>155</v>
       </c>
-      <c r="C154" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
+      <c r="B156" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C156" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
         <v>156</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="B157" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="C157" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
         <v>157</v>
       </c>
-      <c r="C156" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="B158" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="C158" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
         <v>158</v>
       </c>
-      <c r="C157" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="B159" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C159" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
         <v>159</v>
       </c>
-      <c r="C158" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="B160" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="C160" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
         <v>160</v>
       </c>
-      <c r="C159" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="B161" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="C161" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
         <v>161</v>
       </c>
-      <c r="C160" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="B162" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="C162" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
         <v>162</v>
       </c>
-      <c r="C161" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="B163" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C163" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="C162" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
+      <c r="B164" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C164" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
         <v>164</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="B165" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C165" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
         <v>165</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="B166" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="C166" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
         <v>166</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+      <c r="B167" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="C167" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
         <v>167</v>
       </c>
-      <c r="C166" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+      <c r="B168" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="C168" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
         <v>168</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+      <c r="B169" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="C169" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
         <v>169</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+      <c r="B170" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="C170" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
         <v>170</v>
       </c>
-      <c r="C169" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
+      <c r="B171" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="C171" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
         <v>171</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
+      <c r="B172" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="C172" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
         <v>172</v>
       </c>
-      <c r="C171" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="B173" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="C173" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
         <v>173</v>
       </c>
-      <c r="C172" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
+      <c r="B174" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="C174" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
         <v>174</v>
       </c>
-      <c r="C173" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="B175" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="C175" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
         <v>175</v>
       </c>
-      <c r="C174" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+      <c r="B176" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B175" s="2" t="s">
+      <c r="C176" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
         <v>176</v>
       </c>
-      <c r="C175" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="B177" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="C177" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
         <v>177</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+      <c r="B178" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="C178" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
         <v>178</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+      <c r="B179" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="C179" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
         <v>179</v>
       </c>
-      <c r="C178" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+      <c r="B180" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="C180" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
         <v>180</v>
       </c>
-      <c r="C179" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+      <c r="B181" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="C181" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
         <v>181</v>
       </c>
-      <c r="C180" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+      <c r="B182" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="C182" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
         <v>182</v>
       </c>
-      <c r="C181" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
+      <c r="B183" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="C183" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
         <v>183</v>
       </c>
-      <c r="C182" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="B184" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="C184" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
         <v>184</v>
       </c>
-      <c r="C183" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
+      <c r="B185" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="C185" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
         <v>185</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="B186" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C186" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B185" s="2" t="s">
+      <c r="C187" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C188" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C185" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
-        <v>185</v>
-      </c>
-      <c r="B186" s="2" t="s">
+      <c r="C189" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C186" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>186</v>
-      </c>
-      <c r="B187" s="2" t="s">
+      <c r="C190" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C187" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
-        <v>187</v>
-      </c>
-      <c r="B188" s="2" t="s">
+      <c r="C191" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>188</v>
-      </c>
-      <c r="B189" s="2" t="s">
+      <c r="C192" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C189" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
-        <v>189</v>
-      </c>
-      <c r="B190" s="2" t="s">
+      <c r="C193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C190" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
-        <v>190</v>
-      </c>
-      <c r="B191" s="2" t="s">
+      <c r="C194" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C191" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
-        <v>191</v>
-      </c>
-      <c r="B192" s="2" t="s">
+      <c r="C195" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
-        <v>192</v>
-      </c>
-      <c r="B193" s="2" t="s">
+      <c r="C196" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C197" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
-        <v>193</v>
-      </c>
-      <c r="B194" s="2" t="s">
+      <c r="C198" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C194" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
-        <v>194</v>
-      </c>
-      <c r="B195" s="2" t="s">
+      <c r="C199" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C195" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
-        <v>195</v>
-      </c>
-      <c r="B196" s="2" t="s">
+      <c r="C200" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C196" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
-        <v>196</v>
-      </c>
-      <c r="B197" s="2" t="s">
+      <c r="C201" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C197" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
-        <v>197</v>
-      </c>
-      <c r="B198" s="2" t="s">
+      <c r="C202" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C198" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
-        <v>198</v>
-      </c>
-      <c r="B199" s="2" t="s">
+      <c r="C203" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
-        <v>199</v>
-      </c>
-      <c r="B200" s="2" t="s">
+      <c r="C204" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C200" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
-        <v>200</v>
-      </c>
-      <c r="B201" s="2" t="s">
+      <c r="C205" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C201" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
-        <v>201</v>
-      </c>
-      <c r="B202" s="2" t="s">
+      <c r="C206" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C202" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
-        <v>202</v>
-      </c>
-      <c r="B203" s="2" t="s">
+      <c r="C207" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C203" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
-        <v>203</v>
-      </c>
-      <c r="B204" s="2" t="s">
+      <c r="C208" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
-        <v>204</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
-        <v>205</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
-        <v>206</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
-        <v>207</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
-        <v>208</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>211</v>
+      <c r="C209" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_13.xlsx
+++ b/Cardiologie/Excel/cardio_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009F1B04-ACF9-4A5A-BC15-F888E31896F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC2F080-D5B5-4E64-8F05-8FE245FAA6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="423">
   <si>
     <t>Les acrosyndromes vasculaires sont toujours secondaires à une autre pathologie vasculaire.</t>
   </si>
@@ -658,13 +658,637 @@
     <t>Justification</t>
   </si>
   <si>
-    <t>Reference</t>
-  </si>
-  <si>
     <t>Question</t>
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le terme désigne toute condition, primitive ou secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document distingue les formes paroxystiques des formes permanentes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont tous deux listés dans la colonne des acrosyndromes permanents </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se manifeste par une sensation de froid permanente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La symptomatologie est effectivement indolore mais parfois socialement invalidante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle implique une hypertonie sympathique et une stase capillaro-veinulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche principalement la femme jeune de moins de 30 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aucun examen n'est habituellement requis sauf capillaroscopie si Raynaud surajouté </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme qu'il n'existe aucun traitement médicamenteux pour l'améliorer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut être traitée par ionophorèse ou injections sous-cutanées de toxine botulinique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne explicitement : "syndrome des paumes rouges (syndrome de Lane)" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il doit être différencié de l'érythème palmaire acquis lié à la cirrhose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est effectivement le plus fréquent des acrosyndromes vasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document indique que leur prévalence globale est d'au moins 10 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrorhigose est effectivement parfois associée à l'hypothyroïdie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles trophiques sont décrits comme rarissimes dans la forme primaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sclérodermie (&gt;90% - CREST) est fréquemment associée à ce syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ils sont au contraire les médicaments les plus souvent incriminés dans sa genèse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes s'améliorent au contraire au froid (immersion eau froide) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se définit par une cyanose et une froideur permanente des extrémités </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La forme neurologique est effectivement la plus fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'étiologie cite le muscle petit pectoral et non le grand pectoral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'apparition ou l'aggravation des plaintes survient à l'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles touchent la partie distale des membres ou les zones exposées (nez, oreilles…) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles s'observent au contraire quand les fluides tissulaires ne gèlent pas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement comprend réchauffement, aspirine (75mg/j) et ibuprofène (800mg/j) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise qu'il n'y a ni bilan ni traitement spécifique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrocyanose est au contraire décrite comme étant non douloureuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo primaire apparaît et disparaît indépendamment de la température </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement est d'abord étiologique, protecteur (froid, tabac) et médicamenteux </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles s'observent quand la température reste basse pendant plusieurs heures ou jours </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles touchent effectivement la partie distale des membres et les zones exposées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont citées comme touchant notamment les personnes sans-abris </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hématome disparaîtra spontanément en quelques jours (et non semaines) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est décrite comme une sensation de froid permanente et indolore </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est liée à une rupture d’une veine de doigt (et non d'une artère) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrorhigose prédomine chez la femme jeune </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition exacte donnée dans l'introduction du chapitre </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte indique au contraire une prévalence globale d'au moins 10 % </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le phénomène est effectivement rarement observé au cabinet de consultation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont les engelures qui sont souvent confondues avec d'autres pathologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est classée parmi les acrosyndromes liés à une vasoconstriction (hypodébit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est effectivement liée à une vasoconstriction (hypodébit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo est classé dans la colonne vasoconstriction (hypodébit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrocholose est classée dans la colonne vasodilatation (hyperhémie) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont listées dans la colonne des acrosyndromes paroxystiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est classé parmi les syndromes liés à une vasoconstriction (hypodébit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise qu'elle prédomine chez la femme jeune </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est liée à une hypertonie sympathique et non parasympathique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est une affection bénigne parfois associée à l'hypothyroïdie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anomalies artérielles sont absentes dans la maladie de Raynaud (forme primaire) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrocyanose se définit par une froideur et une cyanose permanente, accentuées au froid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'acrocyanose qui est souvent associée à une hyperhidrose, pas l'acrorhigose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut révéler une maladie de Vaquez ou une thrombocytémie essentielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que les symptômes de l'acrocyanose s’accentuent à l’exposition au froid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise qu'elle est essentielle (primitive) dans la plupart des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document indique que dans la plupart des cas, il s’agit d’une acrocyanose essentielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle touche effectivement la femme jeune de moins de 30 ans et débute à l’adolescence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que cette pathologie touche des femmes minces </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se manifeste par des mains/pieds bleu-violets, froids, oedémateux et moites </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le diagnostic se fait sur base de la clinique ; aucun examen n'est habituellement requis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen étudie les capillaires mais le texte ne précise pas la localisation sur l'index </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement repose sur l'arrêt du tabac et la prévention contre le froid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’hyperhidrose (associée à l'acrocyanose) peut être traitée par ionophorèse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette chirurgie est réservée à l’hyperhidrose palmaire sévère et invalidante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le livedo physiologique qui apparaît au froid et disparaît au réchauffement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo est une érythrocyanose en réseau d’origine vasculaire (pas neurologique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le reticularis est en mailles de filet et le racemosa présente des ramifications </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La physiopathologie implique une désoxygénation et/ou une stase sanguine des plexus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est causé par une diminution du flux artériolaire (et non une augmentation) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une résistance augmentée au flux veineux est une cause citée de livedo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est très fréquent chez le nouveau-né et plus fréquent chez les prématurés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il touche au contraire très fréquemment les femmes ou jeunes filles à la peau claire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le livedo physiologique qui présente cette caractéristique thermique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes des érythermalgies sont au contraire améliorés par le froid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que le livedo chez les trisomiques peut fluctuer selon l’âge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le cutis marmorata est le nom latin du livedo physiologique (peau marbrée) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne le livedo physiologique comme étant fréquent dans ce groupe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo idiopathique touche typiquement les femmes (et non les hommes) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il est précisé qu'il n'y a pas de traitement spécifique du livedo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo primaire est effectivement défini comme un diagnostic d’exclusion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo idiopathique est décrit comme persistant sans cause sous-jacente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est le livedo physiologique qui disparaît complètement au réchauffement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo racemosa (ramifications) est cité dans la catégorie des livedos secondaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le livedo physiologique (et non secondaire) disparaît au réchauffement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes ces pathologies sont listées comme des causes de livedo secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les infections sont citées parmi les étiologies possibles du livedo secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces deux conditions sont citées comme causes possibles de livedo secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrocholose est décrite comme l'inverse du Raynaud (hyperhémie vs vasoconstriction) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrocholose est effectivement décrite comme une affection bénigne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acrocholose se manifeste par des sensations de brûlure (pas de chaleur mentionnée) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il faut effectivement exclure une neuropathie périphérique sous-jacente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont des manifestations fonctionnelles (subjectives) sans signe clinique objectif évident </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anomalie est due à des capillaires disposés parallèlement à la peau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les capillaires sont disposés parallèlement (et non perpendiculairement) à la peau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Lane réalise effectivement un tableau permanent d’érythème palmaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'érythème palmaire acquis est effectivement associé à la grossesse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La suite est : blanc (syncopale), puis bleu (asphyxique), puis rouge (hyperhémique) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le blanchissement est distal (au niveau des doigts/orteils) et non proximal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La phase asphyxique se caractérise effectivement par une cyanose des doigts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La phase hyperhémique est habituellement la troisième phase, après les phases syncopale et asphyxique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'apparition d'une érythrose douloureuse caractérise effectivement la phase hyperhémique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La physiopathologie implique une augmentation de la vasomotricité distale d'origine orthosympathique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le phénomène de Raynaud secondaire est appelé syndrome de Raynaud (la maladie est la forme primaire) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Raynaud (forme secondaire) peut être le témoin d'une pathologie grave sous-jacente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Raynaud (forme primaire) est explicitement décrite comme bénigne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Raynaud touche autant les hommes que les femmes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Raynaud (forme primaire) débute au contraire souvent avant 40 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La distribution des symptômes de la maladie de Raynaud épargne effectivement les pouces </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La distribution des symptômes dans le syndrome de Raynaud est parfois bilatérale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les anomalies artérielles sont au contraire notées comme absentes dans la maladie de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles trophiques sont décrits comme fréquents dans le syndrome de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La capillaroscopie est au contraire décrite comme normale dans la maladie de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le pronostic de la maladie de Raynaud (forme primaire) est effectivement excellent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Raynaud peut effectivement débuter à tout âge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les examens de laboratoire peuvent être au contraire anormaux dans le syndrome de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La maladie de Raynaud touche 4 femmes pour 1 homme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise que la maladie de Raynaud touche 4 femmes pour 1 homme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sclérodermie est citée comme étant associée à un phénomène de Raynaud dans plus de 90% des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'association au lupus, Sjögren ou polyarthrite est au contraire décrite comme moins fréquente que pour la sclérodermie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les troubles de la mobilité oesophagienne font partie de la description de la forme CREST </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte confirme que la sclérodermie (forme CREST) est associée au Raynaud dans &gt;90% des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste précisément ces manifestations pour la forme CREST </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne mentionne pas la disparition des télangiectasies à la vitropression </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte associe ces signes à la sclérodermie (forme CREST) et non au lupus </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome de Raynaud peut effectivement être associé à ces deux étiologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les bêtabloquants sont au contraire les médicaments les plus souvent incriminés dans l'exacerbation du phénomène </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome du défilé thoraco-brachial est cité comme une étiologie possible d'artériopathie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome du canal carpien est effectivement cité comme un exemple de compression neurologique causant un Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des traitements médicamenteux comme les antagonistes calciques (nifédipine) sont proposés en cas d'invalidité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces facteurs traumatiques peuvent effectivement engendrer un phénomène de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anévrisme cubital lié au volley-ball est cité comme une cause traumatique de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les dérivés de l'ergot et certains antimitotiques (bléiomycine) sont des sources citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que les bêtabloquants sont les médicaments les plus incriminés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'arrêt du tabac et la protection contre le froid sont des recommandations thérapeutiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'association au lupus ou à la polyarthrite est décrite comme moins fréquente que pour la sclérodermie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne les agglutinines froides (et non chaudes), la cryofibrinogénémie et la cryoglobulinémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La nifédipine est citée comme exemple d'antagoniste calcique efficace </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois effets secondaires sont explicitement mentionnés pour les antagonistes calciques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que les médicaments (dont la nifédipine) sont proposés en cas d'invalidité importante </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les érythermalgies sont effectivement décrites comme l'inverse du phénomène de Raynaud </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont au contraire paroxystiques et aggravées par la position déclive (au coucher) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document définit les érythermalgies par ces deux caractéristiques cliniques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'affection est décrite comme étant paroxystique (et non permanente) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme l'amélioration des symptômes par le froid ou la surélévation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document cite des troubles de l'agrégation plaquettaire, pas de la coagulation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les érythermalgies sont probablement liées à des troubles du métabolisme des prostaglandines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que l'affection peut être idiopathique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document indique au contraire que ce syndrome est assez rare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition exacte donnée pour l'ensemble des manifestations cliniques du syndrome </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La méga-apophyse transverse peut causer le syndrome mais elle est située au niveau de C7 (pas Th2) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression s'exerce effectivement dans la pince costo-claviculaire entre le muscle et la 1ère côte </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le cal post-fracture de la clavicule est cité comme une cause post-traumatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La côte cervicale est une cause congénitale et non une cause acquise </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition anatomique exacte de l'espace où s'exerce la compression </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les épaules tombantes sont citées comme une cause fonctionnelle par déséquilibre cervico-scapulaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La faiblesse musculaire loco-régionale est au contraire listée comme une cause fonctionnelle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tout déséquilibre de la région cervico-scapulaire est une étiologie fonctionnelle potentielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes peuvent apparaître à l'effort ou lors de la surélévation du bras, sans exclure le repos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression artérielle peut causer un phénomène de Raynaud, mais il est précisé comme unilatéral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La forme neurologique est au contraire décrite comme la plus fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'apparition ou l'aggravation des plaintes se fait effectivement à l'effort </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document mentionne la surélévation prolongée ou répétée du bras (membre supérieur) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La compression artérielle peut au contraire provoquer une ischémie de la main ou des doigts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut provoquer une thrombose ou un anévrisme de l’artère sous-clavière (pas axillaire) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La claudication intermittente du bras est une manifestation de la compression artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La phlébite est une manifestation de la compression veineuse et non artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'œdème de la main suite à une activité physique est un signe de compression veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le syndrome peut causer une fatigabilité ou faiblesse positionnelle du membre supérieur </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les paresthésies surviennent dans les territoires C8-D1 (pas C7) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur est effectivement le signe le plus fréquent quelle que soit l'étiologie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces deux signes sont les manifestations cliniques de la forme neurologique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’examinateur explore au contraire principalement l’axe artériel lors des manœuvres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document ne définit pas cette manœuvre comme le "meilleur" moyen, mais comme une aide </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'apparition d'un souffle sus-claviculaire lors des manœuvres aide effectivement au diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie reste au contraire un sujet de controverse et est réservée à des cas sélectionnés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examinateur recherche la disparition du pouls radial (et non ulnaire) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement repose effectivement sur une rééducation adaptée (musculation des releveurs) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette manœuvre, lorsqu'elle est exagérée, est effectivement souvent positive physiologiquement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document recommande effectivement d'éviter le port de charges lourdes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la description exacte de la manœuvre d'Adson utilisée pour le diagnostic </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont classées parmi les pathologies assimilées aux acrosyndromes vasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles surviennent pendant l’hiver ou le début du printemps </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont effectivement des lésions cutanées inflammatoires liées au froid et à l'humidité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont les gelures qui consistent en une vraie congélation tissulaire, pas les engelures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles surviennent au froid et à l'humidité sans qu'il gèle obligatoirement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont décrites comme des lésions bénignes, fréquentes et saisonnières </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le terrain familial, l'acrocyanose et le Raynaud sont des facteurs favorisants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la description clinique exacte de la lésion initiale de l'engelure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles siègent spécifiquement aux orteils ou aux doigts (extrémités) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les engelures sont effectivement décrites comme prurigineuses et algiques (douloureuses) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles peuvent parfois évoluer vers une ulcération évoquant un trouble ischémique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont au contraire plus fréquentes chez les femmes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'évolution se fait effectivement par poussées de 2 à 4 semaines </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La guérison est spontanée mais la rechute est au contraire possible les années suivantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme qu'il n'y a pas de traitement vraiment efficace </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les vasoconstricteurs doivent être au contraire évités ; les antagonistes calciques sont utiles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que le pronostic est excellent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition pathogénique exacte des gelures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elles sont effectivement décrites comme rares en Belgique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les pré-gelures surviennent effectivement quand la température est proche de -0,5°C pendant plusieurs heures ou jours </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme l'apparition de signes de neuropathie sensitive localisée lors du réchauffement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise au contraire qu'il y a souvent peu de signes objectifs pour ces lésions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette condition d'exposition prolongée est effectivement citée comme contexte favorisant les pré-gelures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aspirine (75 mg/j) et l'ibuprofène (800 mg/j) font partie des médicaments listés pour traiter les gelures </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions sans congélation (pré-gelures) nécessitent au contraire un réchauffement lent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est la définition exacte de l'apoplexie digitale : un hématome digital spontané par rupture veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'affection est décrite comme étant de début brutal (et non progressif) bien que fort douloureuse </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -1035,13 +1659,13 @@
         <v>211</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1053,6 +1677,12 @@
       </c>
       <c r="C2" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1065,6 +1695,12 @@
       <c r="C3" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -1076,6 +1712,12 @@
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1087,6 +1729,12 @@
       <c r="C5" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1098,6 +1746,12 @@
       <c r="C6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1109,6 +1763,12 @@
       <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1120,6 +1780,12 @@
       <c r="C8" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1131,6 +1797,12 @@
       <c r="C9" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1142,6 +1814,12 @@
       <c r="C10" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1153,6 +1831,12 @@
       <c r="C11" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1164,6 +1848,12 @@
       <c r="C12" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D12" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1175,6 +1865,12 @@
       <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="D13" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1186,6 +1882,12 @@
       <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D14" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1197,6 +1899,12 @@
       <c r="C15" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="D15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1208,8 +1916,14 @@
       <c r="C16" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1219,8 +1933,14 @@
       <c r="C17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1230,8 +1950,14 @@
       <c r="C18" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1241,8 +1967,14 @@
       <c r="C19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1252,8 +1984,14 @@
       <c r="C20" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1263,8 +2001,14 @@
       <c r="C21" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1274,8 +2018,14 @@
       <c r="C22" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>234</v>
+      </c>
+      <c r="E22" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1285,8 +2035,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1296,8 +2052,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1307,8 +2069,14 @@
       <c r="C25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1318,8 +2086,14 @@
       <c r="C26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>238</v>
+      </c>
+      <c r="E26" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1329,8 +2103,14 @@
       <c r="C27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>239</v>
+      </c>
+      <c r="E27" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1340,8 +2120,14 @@
       <c r="C28" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>240</v>
+      </c>
+      <c r="E28" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1351,8 +2137,14 @@
       <c r="C29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>241</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1362,8 +2154,14 @@
       <c r="C30" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>242</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1373,8 +2171,14 @@
       <c r="C31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1384,8 +2188,14 @@
       <c r="C32" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>244</v>
+      </c>
+      <c r="E32" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1395,8 +2205,14 @@
       <c r="C33" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1406,8 +2222,14 @@
       <c r="C34" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>246</v>
+      </c>
+      <c r="E34" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1417,8 +2239,14 @@
       <c r="C35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>247</v>
+      </c>
+      <c r="E35" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1428,8 +2256,14 @@
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>248</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1439,8 +2273,14 @@
       <c r="C37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1450,8 +2290,14 @@
       <c r="C38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>250</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1461,8 +2307,14 @@
       <c r="C39" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1472,8 +2324,14 @@
       <c r="C40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>252</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1483,8 +2341,14 @@
       <c r="C41" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>253</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1494,8 +2358,14 @@
       <c r="C42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>254</v>
+      </c>
+      <c r="E42" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1505,8 +2375,14 @@
       <c r="C43" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>255</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1516,8 +2392,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>256</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1527,8 +2409,14 @@
       <c r="C45" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>257</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1538,8 +2426,14 @@
       <c r="C46" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>258</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1549,8 +2443,14 @@
       <c r="C47" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>259</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1560,8 +2460,14 @@
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1571,8 +2477,14 @@
       <c r="C49" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>261</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1582,8 +2494,14 @@
       <c r="C50" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>262</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1593,8 +2511,14 @@
       <c r="C51" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>263</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1604,8 +2528,14 @@
       <c r="C52" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>264</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1615,8 +2545,14 @@
       <c r="C53" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>265</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1626,8 +2562,14 @@
       <c r="C54" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1637,8 +2579,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1648,8 +2596,14 @@
       <c r="C56" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>268</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1659,8 +2613,14 @@
       <c r="C57" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>269</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1670,8 +2630,14 @@
       <c r="C58" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>270</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1681,8 +2647,14 @@
       <c r="C59" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>271</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1692,8 +2664,14 @@
       <c r="C60" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>272</v>
+      </c>
+      <c r="E60" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1703,8 +2681,14 @@
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>273</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1714,8 +2698,14 @@
       <c r="C62" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>274</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1725,8 +2715,14 @@
       <c r="C63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>275</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1736,8 +2732,14 @@
       <c r="C64" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>276</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1747,8 +2749,14 @@
       <c r="C65" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>277</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1758,8 +2766,14 @@
       <c r="C66" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>278</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1769,8 +2783,14 @@
       <c r="C67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>279</v>
+      </c>
+      <c r="E67" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1780,8 +2800,14 @@
       <c r="C68" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>280</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1791,8 +2817,14 @@
       <c r="C69" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>281</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1802,8 +2834,14 @@
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>282</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1813,8 +2851,14 @@
       <c r="C71" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>283</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1824,8 +2868,14 @@
       <c r="C72" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1835,8 +2885,14 @@
       <c r="C73" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>285</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1846,8 +2902,14 @@
       <c r="C74" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>286</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1857,8 +2919,14 @@
       <c r="C75" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>287</v>
+      </c>
+      <c r="E75" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1868,8 +2936,14 @@
       <c r="C76" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>288</v>
+      </c>
+      <c r="E76" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1879,8 +2953,14 @@
       <c r="C77" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>289</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1890,8 +2970,14 @@
       <c r="C78" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>290</v>
+      </c>
+      <c r="E78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1901,8 +2987,14 @@
       <c r="C79" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>291</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1912,8 +3004,14 @@
       <c r="C80" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>292</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1923,8 +3021,14 @@
       <c r="C81" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>293</v>
+      </c>
+      <c r="E81" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1934,8 +3038,14 @@
       <c r="C82" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>294</v>
+      </c>
+      <c r="E82" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1945,8 +3055,14 @@
       <c r="C83" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>295</v>
+      </c>
+      <c r="E83" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1956,8 +3072,14 @@
       <c r="C84" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>296</v>
+      </c>
+      <c r="E84" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1967,8 +3089,14 @@
       <c r="C85" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>297</v>
+      </c>
+      <c r="E85" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1978,8 +3106,14 @@
       <c r="C86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>298</v>
+      </c>
+      <c r="E86" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1989,8 +3123,14 @@
       <c r="C87" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>299</v>
+      </c>
+      <c r="E87" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2000,8 +3140,14 @@
       <c r="C88" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>300</v>
+      </c>
+      <c r="E88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2011,8 +3157,14 @@
       <c r="C89" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>301</v>
+      </c>
+      <c r="E89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2022,8 +3174,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>302</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2033,8 +3191,14 @@
       <c r="C91" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>303</v>
+      </c>
+      <c r="E91" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2044,8 +3208,14 @@
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>304</v>
+      </c>
+      <c r="E92" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2055,8 +3225,14 @@
       <c r="C93" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>305</v>
+      </c>
+      <c r="E93" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2066,8 +3242,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>306</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2077,8 +3259,14 @@
       <c r="C95" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>307</v>
+      </c>
+      <c r="E95" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2088,8 +3276,14 @@
       <c r="C96" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>308</v>
+      </c>
+      <c r="E96" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2099,8 +3293,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>309</v>
+      </c>
+      <c r="E97" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2110,8 +3310,14 @@
       <c r="C98" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>310</v>
+      </c>
+      <c r="E98" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2121,8 +3327,14 @@
       <c r="C99" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>311</v>
+      </c>
+      <c r="E99" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2132,8 +3344,14 @@
       <c r="C100" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>312</v>
+      </c>
+      <c r="E100" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2143,8 +3361,14 @@
       <c r="C101" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>313</v>
+      </c>
+      <c r="E101" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2154,8 +3378,14 @@
       <c r="C102" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>314</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2165,8 +3395,14 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>315</v>
+      </c>
+      <c r="E103" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2176,8 +3412,14 @@
       <c r="C104" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>316</v>
+      </c>
+      <c r="E104" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2187,8 +3429,14 @@
       <c r="C105" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>317</v>
+      </c>
+      <c r="E105" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -2198,8 +3446,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>318</v>
+      </c>
+      <c r="E106" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2209,8 +3463,14 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>319</v>
+      </c>
+      <c r="E107" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2220,8 +3480,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>320</v>
+      </c>
+      <c r="E108" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2231,8 +3497,14 @@
       <c r="C109" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>321</v>
+      </c>
+      <c r="E109" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2242,8 +3514,14 @@
       <c r="C110" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>322</v>
+      </c>
+      <c r="E110" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2253,8 +3531,14 @@
       <c r="C111" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>323</v>
+      </c>
+      <c r="E111" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2264,8 +3548,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>324</v>
+      </c>
+      <c r="E112" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2275,8 +3565,14 @@
       <c r="C113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>325</v>
+      </c>
+      <c r="E113" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2286,8 +3582,14 @@
       <c r="C114" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>326</v>
+      </c>
+      <c r="E114" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2297,8 +3599,14 @@
       <c r="C115" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>327</v>
+      </c>
+      <c r="E115" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2308,8 +3616,14 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>328</v>
+      </c>
+      <c r="E116" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2319,8 +3633,14 @@
       <c r="C117" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>329</v>
+      </c>
+      <c r="E117" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2330,8 +3650,14 @@
       <c r="C118" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>330</v>
+      </c>
+      <c r="E118" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2341,8 +3667,14 @@
       <c r="C119" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>331</v>
+      </c>
+      <c r="E119" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2352,8 +3684,14 @@
       <c r="C120" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>332</v>
+      </c>
+      <c r="E120" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2363,8 +3701,14 @@
       <c r="C121" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>333</v>
+      </c>
+      <c r="E121" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2374,8 +3718,14 @@
       <c r="C122" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>334</v>
+      </c>
+      <c r="E122" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2385,8 +3735,14 @@
       <c r="C123" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>335</v>
+      </c>
+      <c r="E123" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2396,8 +3752,14 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>336</v>
+      </c>
+      <c r="E124" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2407,8 +3769,14 @@
       <c r="C125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>337</v>
+      </c>
+      <c r="E125" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2418,8 +3786,14 @@
       <c r="C126" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>338</v>
+      </c>
+      <c r="E126" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2429,8 +3803,14 @@
       <c r="C127" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" t="s">
+        <v>339</v>
+      </c>
+      <c r="E127" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -2440,8 +3820,14 @@
       <c r="C128" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" t="s">
+        <v>340</v>
+      </c>
+      <c r="E128" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -2451,8 +3837,14 @@
       <c r="C129" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" t="s">
+        <v>341</v>
+      </c>
+      <c r="E129" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -2462,8 +3854,14 @@
       <c r="C130" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" t="s">
+        <v>342</v>
+      </c>
+      <c r="E130" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -2473,8 +3871,14 @@
       <c r="C131" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" t="s">
+        <v>343</v>
+      </c>
+      <c r="E131" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -2484,8 +3888,14 @@
       <c r="C132" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" t="s">
+        <v>344</v>
+      </c>
+      <c r="E132" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -2495,8 +3905,14 @@
       <c r="C133" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" t="s">
+        <v>345</v>
+      </c>
+      <c r="E133" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -2506,8 +3922,14 @@
       <c r="C134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" t="s">
+        <v>346</v>
+      </c>
+      <c r="E134" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -2517,8 +3939,14 @@
       <c r="C135" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" t="s">
+        <v>347</v>
+      </c>
+      <c r="E135" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -2528,8 +3956,14 @@
       <c r="C136" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" t="s">
+        <v>348</v>
+      </c>
+      <c r="E136" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -2539,8 +3973,14 @@
       <c r="C137" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" t="s">
+        <v>349</v>
+      </c>
+      <c r="E137" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -2550,8 +3990,14 @@
       <c r="C138" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" t="s">
+        <v>350</v>
+      </c>
+      <c r="E138" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -2561,8 +4007,14 @@
       <c r="C139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" t="s">
+        <v>351</v>
+      </c>
+      <c r="E139" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -2572,8 +4024,14 @@
       <c r="C140" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" t="s">
+        <v>352</v>
+      </c>
+      <c r="E140" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -2583,8 +4041,14 @@
       <c r="C141" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" t="s">
+        <v>353</v>
+      </c>
+      <c r="E141" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -2594,8 +4058,14 @@
       <c r="C142" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" t="s">
+        <v>354</v>
+      </c>
+      <c r="E142" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -2605,8 +4075,14 @@
       <c r="C143" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" t="s">
+        <v>355</v>
+      </c>
+      <c r="E143" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -2616,8 +4092,14 @@
       <c r="C144" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" t="s">
+        <v>356</v>
+      </c>
+      <c r="E144" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -2627,8 +4109,14 @@
       <c r="C145" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" t="s">
+        <v>357</v>
+      </c>
+      <c r="E145" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -2638,8 +4126,14 @@
       <c r="C146" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" t="s">
+        <v>358</v>
+      </c>
+      <c r="E146" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -2649,8 +4143,14 @@
       <c r="C147" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" t="s">
+        <v>359</v>
+      </c>
+      <c r="E147" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -2660,8 +4160,14 @@
       <c r="C148" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" t="s">
+        <v>360</v>
+      </c>
+      <c r="E148" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -2671,8 +4177,14 @@
       <c r="C149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" t="s">
+        <v>361</v>
+      </c>
+      <c r="E149" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -2682,8 +4194,14 @@
       <c r="C150" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" t="s">
+        <v>362</v>
+      </c>
+      <c r="E150" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -2693,8 +4211,14 @@
       <c r="C151" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" t="s">
+        <v>363</v>
+      </c>
+      <c r="E151" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -2704,8 +4228,14 @@
       <c r="C152" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" t="s">
+        <v>364</v>
+      </c>
+      <c r="E152" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -2715,8 +4245,14 @@
       <c r="C153" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" t="s">
+        <v>365</v>
+      </c>
+      <c r="E153" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -2726,8 +4262,14 @@
       <c r="C154" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" t="s">
+        <v>366</v>
+      </c>
+      <c r="E154" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -2737,8 +4279,14 @@
       <c r="C155" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" t="s">
+        <v>367</v>
+      </c>
+      <c r="E155" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -2748,8 +4296,14 @@
       <c r="C156" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" t="s">
+        <v>368</v>
+      </c>
+      <c r="E156" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -2759,8 +4313,14 @@
       <c r="C157" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" t="s">
+        <v>369</v>
+      </c>
+      <c r="E157" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -2770,8 +4330,14 @@
       <c r="C158" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" t="s">
+        <v>370</v>
+      </c>
+      <c r="E158" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -2781,8 +4347,14 @@
       <c r="C159" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" t="s">
+        <v>371</v>
+      </c>
+      <c r="E159" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -2792,8 +4364,14 @@
       <c r="C160" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" t="s">
+        <v>372</v>
+      </c>
+      <c r="E160" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -2803,8 +4381,14 @@
       <c r="C161" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" t="s">
+        <v>373</v>
+      </c>
+      <c r="E161" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -2814,8 +4398,14 @@
       <c r="C162" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" t="s">
+        <v>374</v>
+      </c>
+      <c r="E162" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -2825,8 +4415,14 @@
       <c r="C163" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" t="s">
+        <v>375</v>
+      </c>
+      <c r="E163" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -2836,8 +4432,14 @@
       <c r="C164" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" t="s">
+        <v>376</v>
+      </c>
+      <c r="E164" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -2847,8 +4449,14 @@
       <c r="C165" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" t="s">
+        <v>377</v>
+      </c>
+      <c r="E165" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -2858,8 +4466,14 @@
       <c r="C166" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" t="s">
+        <v>378</v>
+      </c>
+      <c r="E166" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -2869,8 +4483,14 @@
       <c r="C167" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" t="s">
+        <v>379</v>
+      </c>
+      <c r="E167" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -2880,8 +4500,14 @@
       <c r="C168" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" t="s">
+        <v>380</v>
+      </c>
+      <c r="E168" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -2891,8 +4517,14 @@
       <c r="C169" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" t="s">
+        <v>381</v>
+      </c>
+      <c r="E169" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -2902,8 +4534,14 @@
       <c r="C170" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" t="s">
+        <v>382</v>
+      </c>
+      <c r="E170" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -2913,8 +4551,14 @@
       <c r="C171" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" t="s">
+        <v>383</v>
+      </c>
+      <c r="E171" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -2924,8 +4568,14 @@
       <c r="C172" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" t="s">
+        <v>384</v>
+      </c>
+      <c r="E172" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -2935,8 +4585,14 @@
       <c r="C173" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" t="s">
+        <v>385</v>
+      </c>
+      <c r="E173" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -2946,8 +4602,14 @@
       <c r="C174" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" t="s">
+        <v>386</v>
+      </c>
+      <c r="E174" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -2957,8 +4619,14 @@
       <c r="C175" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" t="s">
+        <v>387</v>
+      </c>
+      <c r="E175" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -2968,8 +4636,14 @@
       <c r="C176" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" t="s">
+        <v>388</v>
+      </c>
+      <c r="E176" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -2979,8 +4653,14 @@
       <c r="C177" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" t="s">
+        <v>389</v>
+      </c>
+      <c r="E177" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -2990,8 +4670,14 @@
       <c r="C178" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" t="s">
+        <v>390</v>
+      </c>
+      <c r="E178" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -3001,8 +4687,14 @@
       <c r="C179" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" t="s">
+        <v>391</v>
+      </c>
+      <c r="E179" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -3012,8 +4704,14 @@
       <c r="C180" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" t="s">
+        <v>392</v>
+      </c>
+      <c r="E180" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -3023,8 +4721,14 @@
       <c r="C181" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" t="s">
+        <v>393</v>
+      </c>
+      <c r="E181" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -3034,8 +4738,14 @@
       <c r="C182" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" t="s">
+        <v>394</v>
+      </c>
+      <c r="E182" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -3045,8 +4755,14 @@
       <c r="C183" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" t="s">
+        <v>395</v>
+      </c>
+      <c r="E183" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -3056,8 +4772,14 @@
       <c r="C184" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" t="s">
+        <v>396</v>
+      </c>
+      <c r="E184" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -3067,8 +4789,14 @@
       <c r="C185" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" t="s">
+        <v>397</v>
+      </c>
+      <c r="E185" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -3078,8 +4806,14 @@
       <c r="C186" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" t="s">
+        <v>398</v>
+      </c>
+      <c r="E186" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -3089,8 +4823,14 @@
       <c r="C187" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" t="s">
+        <v>399</v>
+      </c>
+      <c r="E187" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -3100,8 +4840,14 @@
       <c r="C188" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" t="s">
+        <v>400</v>
+      </c>
+      <c r="E188" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -3111,8 +4857,14 @@
       <c r="C189" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" t="s">
+        <v>401</v>
+      </c>
+      <c r="E189" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -3122,8 +4874,14 @@
       <c r="C190" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" t="s">
+        <v>402</v>
+      </c>
+      <c r="E190" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -3133,8 +4891,14 @@
       <c r="C191" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" t="s">
+        <v>403</v>
+      </c>
+      <c r="E191" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -3144,8 +4908,14 @@
       <c r="C192" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" t="s">
+        <v>404</v>
+      </c>
+      <c r="E192" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -3155,8 +4925,14 @@
       <c r="C193" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" t="s">
+        <v>405</v>
+      </c>
+      <c r="E193" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -3166,8 +4942,14 @@
       <c r="C194" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" t="s">
+        <v>406</v>
+      </c>
+      <c r="E194" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -3177,8 +4959,14 @@
       <c r="C195" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" t="s">
+        <v>407</v>
+      </c>
+      <c r="E195" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -3188,8 +4976,14 @@
       <c r="C196" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" t="s">
+        <v>408</v>
+      </c>
+      <c r="E196" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -3199,8 +4993,14 @@
       <c r="C197" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" t="s">
+        <v>409</v>
+      </c>
+      <c r="E197" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -3210,8 +5010,14 @@
       <c r="C198" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" t="s">
+        <v>410</v>
+      </c>
+      <c r="E198" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -3221,8 +5027,14 @@
       <c r="C199" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" t="s">
+        <v>411</v>
+      </c>
+      <c r="E199" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -3232,8 +5044,14 @@
       <c r="C200" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" t="s">
+        <v>412</v>
+      </c>
+      <c r="E200" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -3243,8 +5061,14 @@
       <c r="C201" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" t="s">
+        <v>413</v>
+      </c>
+      <c r="E201" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -3254,8 +5078,14 @@
       <c r="C202" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" t="s">
+        <v>414</v>
+      </c>
+      <c r="E202" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -3265,8 +5095,14 @@
       <c r="C203" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203" t="s">
+        <v>415</v>
+      </c>
+      <c r="E203" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -3276,8 +5112,14 @@
       <c r="C204" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204" t="s">
+        <v>416</v>
+      </c>
+      <c r="E204" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -3287,8 +5129,14 @@
       <c r="C205" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205" t="s">
+        <v>417</v>
+      </c>
+      <c r="E205" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -3298,8 +5146,14 @@
       <c r="C206" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206" t="s">
+        <v>418</v>
+      </c>
+      <c r="E206" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -3309,8 +5163,14 @@
       <c r="C207" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207" t="s">
+        <v>419</v>
+      </c>
+      <c r="E207" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -3320,8 +5180,14 @@
       <c r="C208" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208" t="s">
+        <v>420</v>
+      </c>
+      <c r="E208" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -3330,6 +5196,12 @@
       </c>
       <c r="C209" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="D209" t="s">
+        <v>421</v>
+      </c>
+      <c r="E209" s="1">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
